--- a/artfynd/A 56759-2025 artfynd.xlsx
+++ b/artfynd/A 56759-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,32 +680,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79745506</v>
+        <v>137446171</v>
       </c>
       <c r="B2" t="n">
-        <v>92564</v>
+        <v>92982</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,17 +714,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ängfors O, Vstm</t>
+          <t>Ängfors, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567558</v>
+        <v>567549</v>
       </c>
       <c r="R2" t="n">
-        <v>6613864</v>
+        <v>6613797</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,12 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-09-04</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-09-04</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,12 +768,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Äldre granskog, inslag av lövträd, hassel</t>
+          <t>Blandskog, hassel</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Gran, med klibbticka</t>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -790,38 +790,38 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79745506</t>
+          <t>https://artportalen.se/Sighting/137446171</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79745550</v>
+        <v>137446380</v>
       </c>
       <c r="B3" t="n">
-        <v>92564</v>
+        <v>92982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -830,14 +830,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ängfors NO, Vstm</t>
+          <t>Ängfors, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567612</v>
+        <v>567542</v>
       </c>
       <c r="R3" t="n">
-        <v>6613999</v>
+        <v>6613766</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,12 +864,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-09-04</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-09-04</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,18 +878,17 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Äldre granskog, inslag av lövträd, hassel</t>
+          <t>Betesmark</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Gran, med klibbticka</t>
+          <t>Asplåga i betesmark</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -906,13 +905,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79745550</t>
+          <t>https://artportalen.se/Sighting/137446380</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>79745615</v>
+        <v>79745506</v>
       </c>
       <c r="B4" t="n">
         <v>92564</v>
@@ -946,14 +945,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ängfors NNO, Vstm</t>
+          <t>Ängfors O, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567600</v>
+        <v>567558</v>
       </c>
       <c r="R4" t="n">
-        <v>6614198</v>
+        <v>6613864</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1022,13 +1021,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79745615</t>
+          <t>https://artportalen.se/Sighting/79745506</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>87859462</v>
+        <v>79745550</v>
       </c>
       <c r="B5" t="n">
         <v>92564</v>
@@ -1066,13 +1065,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567634</v>
+        <v>567612</v>
       </c>
       <c r="R5" t="n">
-        <v>6614019</v>
+        <v>6613999</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,12 +1095,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-09-06</t>
+          <t>2019-09-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-09-06</t>
+          <t>2019-09-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,12 +1115,12 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrblandskog, inslag av löv</t>
+          <t>Äldre granskog, inslag av lövträd, hassel</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran, med klibbticka</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1138,16 +1137,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87859462</t>
+          <t>https://artportalen.se/Sighting/79745550</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>79746332</v>
+        <v>79745615</v>
       </c>
       <c r="B6" t="n">
-        <v>92632</v>
+        <v>92564</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1154,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>1339</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,14 +1177,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ängfors O, Vstm</t>
+          <t>Ängfors NNO, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567582</v>
+        <v>567600</v>
       </c>
       <c r="R6" t="n">
-        <v>6613913</v>
+        <v>6614198</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,7 +1236,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Gran, basalt</t>
+          <t>Gran, med klibbticka</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1254,65 +1253,57 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79746332</t>
+          <t>https://artportalen.se/Sighting/79745615</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>79745683</v>
+        <v>87859462</v>
       </c>
       <c r="B7" t="n">
-        <v>93215</v>
+        <v>92564</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4368</v>
+        <v>1339</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ängfors O, Vstm</t>
+          <t>Ängfors NO, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567582</v>
+        <v>567634</v>
       </c>
       <c r="R7" t="n">
-        <v>6613913</v>
+        <v>6614019</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1336,12 +1327,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2019-09-04</t>
+          <t>2020-09-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2019-09-04</t>
+          <t>2020-09-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,7 +1347,12 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre granskog, inslag av lövträd, hassel</t>
+          <t>Barrblandskog, inslag av löv</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1372,6 +1368,362 @@
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87859462</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137446328</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92856</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ängfors, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>567573</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6613874</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hallstahammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Svedvi</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Fruktkropp i dåligt skick.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Blandskog, hassel</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137446328</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>79746332</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ängfors O, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>567582</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6613913</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hallstahammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Svedvi</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2019-09-04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2019-09-04</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Äldre granskog, inslag av lövträd, hassel</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Gran, basalt</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79746332</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>79745683</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93215</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ängfors O, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>567582</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6613913</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hallstahammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Svedvi</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2019-09-04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2019-09-04</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Äldre granskog, inslag av lövträd, hassel</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/79745683</t>
         </is>
@@ -1385,6 +1737,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56759-2025 artfynd.xlsx
+++ b/artfynd/A 56759-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137446171</v>
       </c>
       <c r="B2" t="n">
-        <v>92982</v>
+        <v>92985</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137446380</v>
       </c>
       <c r="B3" t="n">
-        <v>92982</v>
+        <v>92985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>137446328</v>
       </c>
       <c r="B8" t="n">
-        <v>92856</v>
+        <v>92859</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 56759-2025 artfynd.xlsx
+++ b/artfynd/A 56759-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137446171</v>
       </c>
       <c r="B2" t="n">
-        <v>92985</v>
+        <v>92989</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137446380</v>
       </c>
       <c r="B3" t="n">
-        <v>92985</v>
+        <v>92989</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>137446328</v>
       </c>
       <c r="B8" t="n">
-        <v>92859</v>
+        <v>92863</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
